--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45316,13 +45316,13 @@
     </row>
     <row r="1649">
       <c r="A1649" s="1" t="n">
-        <v>45940.6494907407</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B1649" t="n">
         <v>111845</v>
       </c>
       <c r="C1649" t="n">
-        <v>5.1399998664856</v>
+        <v>5.15000009536743</v>
       </c>
       <c r="D1649" t="n">
         <v>5.1100001335144</v>
@@ -45337,6 +45337,32 @@
         <v>705</v>
       </c>
       <c r="H1649" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="1" t="n">
+        <v>45943.6511458333</v>
+      </c>
+      <c r="B1650" t="n">
+        <v>44719</v>
+      </c>
+      <c r="C1650" t="n">
+        <v>5.15000009536743</v>
+      </c>
+      <c r="D1650" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="E1650" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="F1650" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="G1650" t="s">
+        <v>703</v>
+      </c>
+      <c r="H1650" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="707">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2130,6 +2130,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.15000009536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11999988555908</t>
   </si>
 </sst>
 </file>
@@ -45342,7 +45345,7 @@
     </row>
     <row r="1650">
       <c r="A1650" s="1" t="n">
-        <v>45943.6511458333</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B1650" t="n">
         <v>44719</v>
@@ -45363,6 +45366,32 @@
         <v>703</v>
       </c>
       <c r="H1650" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="1" t="n">
+        <v>45944.6495486111</v>
+      </c>
+      <c r="B1651" t="n">
+        <v>69484</v>
+      </c>
+      <c r="C1651" t="n">
+        <v>5.13000011444092</v>
+      </c>
+      <c r="D1651" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1651" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="F1651" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="G1651" t="s">
+        <v>706</v>
+      </c>
+      <c r="H1651" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45371,7 +45371,7 @@
     </row>
     <row r="1651">
       <c r="A1651" s="1" t="n">
-        <v>45944.6495486111</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B1651" t="n">
         <v>69484</v>
@@ -45392,6 +45392,32 @@
         <v>706</v>
       </c>
       <c r="H1651" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="1" t="n">
+        <v>45945.6503703704</v>
+      </c>
+      <c r="B1652" t="n">
+        <v>125421</v>
+      </c>
+      <c r="C1652" t="n">
+        <v>5.13000011444092</v>
+      </c>
+      <c r="D1652" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1652" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="F1652" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="G1652" t="s">
+        <v>703</v>
+      </c>
+      <c r="H1652" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45397,7 +45397,7 @@
     </row>
     <row r="1652">
       <c r="A1652" s="1" t="n">
-        <v>45945.6503703704</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B1652" t="n">
         <v>125421</v>
@@ -45418,6 +45418,32 @@
         <v>703</v>
       </c>
       <c r="H1652" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="1" t="n">
+        <v>45946.6493518519</v>
+      </c>
+      <c r="B1653" t="n">
+        <v>62290</v>
+      </c>
+      <c r="C1653" t="n">
+        <v>5.15000009536743</v>
+      </c>
+      <c r="D1653" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="E1653" t="n">
+        <v>5.15000009536743</v>
+      </c>
+      <c r="F1653" t="n">
+        <v>5.13000011444092</v>
+      </c>
+      <c r="G1653" t="s">
+        <v>704</v>
+      </c>
+      <c r="H1653" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="708">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2133,6 +2133,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.11999988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1399998664856</t>
   </si>
 </sst>
 </file>
@@ -45423,7 +45426,7 @@
     </row>
     <row r="1653">
       <c r="A1653" s="1" t="n">
-        <v>45946.6493518519</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B1653" t="n">
         <v>62290</v>
@@ -45444,6 +45447,32 @@
         <v>704</v>
       </c>
       <c r="H1653" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="1" t="n">
+        <v>45947.6493865741</v>
+      </c>
+      <c r="B1654" t="n">
+        <v>73735</v>
+      </c>
+      <c r="C1654" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="D1654" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1654" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F1654" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="G1654" t="s">
+        <v>707</v>
+      </c>
+      <c r="H1654" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45452,7 +45452,7 @@
     </row>
     <row r="1654">
       <c r="A1654" s="1" t="n">
-        <v>45947.6493865741</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B1654" t="n">
         <v>73735</v>
@@ -45473,6 +45473,32 @@
         <v>707</v>
       </c>
       <c r="H1654" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="1" t="n">
+        <v>45950.6494560185</v>
+      </c>
+      <c r="B1655" t="n">
+        <v>22644</v>
+      </c>
+      <c r="C1655" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="D1655" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="E1655" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="F1655" t="n">
+        <v>5.13000011444092</v>
+      </c>
+      <c r="G1655" t="s">
+        <v>704</v>
+      </c>
+      <c r="H1655" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45478,7 +45478,7 @@
     </row>
     <row r="1655">
       <c r="A1655" s="1" t="n">
-        <v>45950.6494560185</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B1655" t="n">
         <v>22644</v>
@@ -45499,6 +45499,32 @@
         <v>704</v>
       </c>
       <c r="H1655" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="1" t="n">
+        <v>45951.6495949074</v>
+      </c>
+      <c r="B1656" t="n">
+        <v>23091</v>
+      </c>
+      <c r="C1656" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="D1656" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="E1656" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="F1656" t="n">
+        <v>5.13000011444092</v>
+      </c>
+      <c r="G1656" t="s">
+        <v>704</v>
+      </c>
+      <c r="H1656" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45504,7 +45504,7 @@
     </row>
     <row r="1656">
       <c r="A1656" s="1" t="n">
-        <v>45951.6495949074</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B1656" t="n">
         <v>23091</v>
@@ -45525,6 +45525,32 @@
         <v>704</v>
       </c>
       <c r="H1656" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="1" t="n">
+        <v>45952.6494444444</v>
+      </c>
+      <c r="B1657" t="n">
+        <v>32492</v>
+      </c>
+      <c r="C1657" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="D1657" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="E1657" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="F1657" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="G1657" t="s">
+        <v>703</v>
+      </c>
+      <c r="H1657" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45530,7 +45530,7 @@
     </row>
     <row r="1657">
       <c r="A1657" s="1" t="n">
-        <v>45952.6494444444</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B1657" t="n">
         <v>32492</v>
@@ -45551,6 +45551,32 @@
         <v>703</v>
       </c>
       <c r="H1657" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="1" t="n">
+        <v>45953.6493981481</v>
+      </c>
+      <c r="B1658" t="n">
+        <v>14221</v>
+      </c>
+      <c r="C1658" t="n">
+        <v>5.13000011444092</v>
+      </c>
+      <c r="D1658" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="E1658" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="F1658" t="n">
+        <v>5.13000011444092</v>
+      </c>
+      <c r="G1658" t="s">
+        <v>704</v>
+      </c>
+      <c r="H1658" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45556,7 +45556,7 @@
     </row>
     <row r="1658">
       <c r="A1658" s="1" t="n">
-        <v>45953.6493981481</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B1658" t="n">
         <v>14221</v>
@@ -45577,6 +45577,32 @@
         <v>704</v>
       </c>
       <c r="H1658" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="1" t="n">
+        <v>45954.6493518519</v>
+      </c>
+      <c r="B1659" t="n">
+        <v>39391</v>
+      </c>
+      <c r="C1659" t="n">
+        <v>5.13000011444092</v>
+      </c>
+      <c r="D1659" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1659" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="F1659" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="G1659" t="s">
+        <v>703</v>
+      </c>
+      <c r="H1659" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45582,7 +45582,7 @@
     </row>
     <row r="1659">
       <c r="A1659" s="1" t="n">
-        <v>45954.6493518519</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B1659" t="n">
         <v>39391</v>
@@ -45603,6 +45603,32 @@
         <v>703</v>
       </c>
       <c r="H1659" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="1" t="n">
+        <v>45957.6911921296</v>
+      </c>
+      <c r="B1660" t="n">
+        <v>11290</v>
+      </c>
+      <c r="C1660" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="D1660" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1660" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="F1660" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="G1660" t="s">
+        <v>702</v>
+      </c>
+      <c r="H1660" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45608,7 +45608,7 @@
     </row>
     <row r="1660">
       <c r="A1660" s="1" t="n">
-        <v>45957.6911921296</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B1660" t="n">
         <v>11290</v>
@@ -45629,6 +45629,32 @@
         <v>702</v>
       </c>
       <c r="H1660" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="1" t="n">
+        <v>45958.6912152778</v>
+      </c>
+      <c r="B1661" t="n">
+        <v>98681</v>
+      </c>
+      <c r="C1661" t="n">
+        <v>5.13000011444092</v>
+      </c>
+      <c r="D1661" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1661" t="n">
+        <v>5.13000011444092</v>
+      </c>
+      <c r="F1661" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="G1661" t="s">
+        <v>702</v>
+      </c>
+      <c r="H1661" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45634,7 +45634,7 @@
     </row>
     <row r="1661">
       <c r="A1661" s="1" t="n">
-        <v>45958.6912152778</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B1661" t="n">
         <v>98681</v>
@@ -45655,6 +45655,32 @@
         <v>702</v>
       </c>
       <c r="H1661" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="1" t="n">
+        <v>45959.6911689815</v>
+      </c>
+      <c r="B1662" t="n">
+        <v>43786</v>
+      </c>
+      <c r="C1662" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="D1662" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1662" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F1662" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="G1662" t="s">
+        <v>703</v>
+      </c>
+      <c r="H1662" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45660,7 +45660,7 @@
     </row>
     <row r="1662">
       <c r="A1662" s="1" t="n">
-        <v>45959.6911689815</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B1662" t="n">
         <v>43786</v>
@@ -45681,6 +45681,32 @@
         <v>703</v>
       </c>
       <c r="H1662" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="1" t="n">
+        <v>45960.6912847222</v>
+      </c>
+      <c r="B1663" t="n">
+        <v>39269</v>
+      </c>
+      <c r="C1663" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="D1663" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1663" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F1663" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="G1663" t="s">
+        <v>702</v>
+      </c>
+      <c r="H1663" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45686,7 +45686,7 @@
     </row>
     <row r="1663">
       <c r="A1663" s="1" t="n">
-        <v>45960.6912847222</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B1663" t="n">
         <v>39269</v>
@@ -45707,6 +45707,32 @@
         <v>702</v>
       </c>
       <c r="H1663" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="1" t="n">
+        <v>45961.6910648148</v>
+      </c>
+      <c r="B1664" t="n">
+        <v>38618</v>
+      </c>
+      <c r="C1664" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="D1664" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="E1664" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F1664" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="G1664" t="s">
+        <v>699</v>
+      </c>
+      <c r="H1664" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45712,7 +45712,7 @@
     </row>
     <row r="1664">
       <c r="A1664" s="1" t="n">
-        <v>45961.6910648148</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B1664" t="n">
         <v>38618</v>
@@ -45733,6 +45733,32 @@
         <v>699</v>
       </c>
       <c r="H1664" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="1" t="n">
+        <v>45964.6911921296</v>
+      </c>
+      <c r="B1665" t="n">
+        <v>21628</v>
+      </c>
+      <c r="C1665" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="D1665" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="E1665" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F1665" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="G1665" t="s">
+        <v>701</v>
+      </c>
+      <c r="H1665" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45738,7 +45738,7 @@
     </row>
     <row r="1665">
       <c r="A1665" s="1" t="n">
-        <v>45964.6911921296</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B1665" t="n">
         <v>21628</v>
@@ -45759,6 +45759,32 @@
         <v>701</v>
       </c>
       <c r="H1665" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="1" t="n">
+        <v>45965.6910648148</v>
+      </c>
+      <c r="B1666" t="n">
+        <v>23761</v>
+      </c>
+      <c r="C1666" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="D1666" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E1666" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1666" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="G1666" t="s">
+        <v>414</v>
+      </c>
+      <c r="H1666" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45764,25 +45764,25 @@
     </row>
     <row r="1666">
       <c r="A1666" s="1" t="n">
-        <v>45965.6910648148</v>
+        <v>45966.6910185185</v>
       </c>
       <c r="B1666" t="n">
-        <v>23761</v>
+        <v>28301</v>
       </c>
       <c r="C1666" t="n">
-        <v>5.09000015258789</v>
+        <v>5.07000017166138</v>
       </c>
       <c r="D1666" t="n">
         <v>5.05000019073486</v>
       </c>
       <c r="E1666" t="n">
-        <v>5.05000019073486</v>
+        <v>5.05999994277954</v>
       </c>
       <c r="F1666" t="n">
-        <v>5.07999992370605</v>
+        <v>5.05999994277954</v>
       </c>
       <c r="G1666" t="s">
-        <v>414</v>
+        <v>699</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45764,27 +45764,53 @@
     </row>
     <row r="1666">
       <c r="A1666" s="1" t="n">
-        <v>45966.6910185185</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B1666" t="n">
-        <v>28301</v>
+        <v>23761</v>
       </c>
       <c r="C1666" t="n">
-        <v>5.07000017166138</v>
+        <v>5.09000015258789</v>
       </c>
       <c r="D1666" t="n">
         <v>5.05000019073486</v>
       </c>
       <c r="E1666" t="n">
-        <v>5.05999994277954</v>
+        <v>5.05000019073486</v>
       </c>
       <c r="F1666" t="n">
-        <v>5.05999994277954</v>
+        <v>5.07999992370605</v>
       </c>
       <c r="G1666" t="s">
-        <v>699</v>
+        <v>414</v>
       </c>
       <c r="H1666" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="1" t="n">
+        <v>45967.6910416667</v>
+      </c>
+      <c r="B1667" t="n">
+        <v>150264</v>
+      </c>
+      <c r="C1667" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="D1667" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1667" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1667" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1667" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1667" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="709">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2136,6 +2136,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.1399998664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03000020980835</t>
   </si>
 </sst>
 </file>
@@ -45790,25 +45793,25 @@
     </row>
     <row r="1667">
       <c r="A1667" s="1" t="n">
-        <v>45967.6910416667</v>
+        <v>45968.6911111111</v>
       </c>
       <c r="B1667" t="n">
-        <v>150264</v>
+        <v>29296</v>
       </c>
       <c r="C1667" t="n">
-        <v>5.07999992370605</v>
+        <v>5.05000019073486</v>
       </c>
       <c r="D1667" t="n">
         <v>5.01999998092651</v>
       </c>
       <c r="E1667" t="n">
-        <v>5.05000019073486</v>
+        <v>5.01999998092651</v>
       </c>
       <c r="F1667" t="n">
-        <v>5.05000019073486</v>
+        <v>5.03000020980835</v>
       </c>
       <c r="G1667" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45793,27 +45793,105 @@
     </row>
     <row r="1667">
       <c r="A1667" s="1" t="n">
-        <v>45968.6911111111</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B1667" t="n">
+        <v>28301</v>
+      </c>
+      <c r="C1667" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="D1667" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E1667" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="F1667" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="G1667" t="s">
+        <v>699</v>
+      </c>
+      <c r="H1667" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B1668" t="n">
+        <v>150264</v>
+      </c>
+      <c r="C1668" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="D1668" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1668" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1668" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1668" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1668" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B1669" t="n">
         <v>29296</v>
       </c>
-      <c r="C1667" t="n">
+      <c r="C1669" t="n">
         <v>5.05000019073486</v>
       </c>
-      <c r="D1667" t="n">
+      <c r="D1669" t="n">
         <v>5.01999998092651</v>
       </c>
-      <c r="E1667" t="n">
+      <c r="E1669" t="n">
         <v>5.01999998092651</v>
       </c>
-      <c r="F1667" t="n">
+      <c r="F1669" t="n">
         <v>5.03000020980835</v>
       </c>
-      <c r="G1667" t="s">
+      <c r="G1669" t="s">
         <v>708</v>
       </c>
-      <c r="H1667" t="s">
+      <c r="H1669" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="1" t="n">
+        <v>45971.6910300926</v>
+      </c>
+      <c r="B1670" t="n">
+        <v>39798</v>
+      </c>
+      <c r="C1670" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="D1670" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1670" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F1670" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1670" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1670" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="710">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2139,6 +2139,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.03000020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01000022888184</t>
   </si>
 </sst>
 </file>
@@ -45871,7 +45874,7 @@
     </row>
     <row r="1670">
       <c r="A1670" s="1" t="n">
-        <v>45971.6910300926</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B1670" t="n">
         <v>39798</v>
@@ -45892,6 +45895,32 @@
         <v>700</v>
       </c>
       <c r="H1670" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="1" t="n">
+        <v>45972.6919675926</v>
+      </c>
+      <c r="B1671" t="n">
+        <v>119672</v>
+      </c>
+      <c r="C1671" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="D1671" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="E1671" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1671" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="G1671" t="s">
+        <v>709</v>
+      </c>
+      <c r="H1671" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45900,7 +45900,7 @@
     </row>
     <row r="1671">
       <c r="A1671" s="1" t="n">
-        <v>45972.6919675926</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B1671" t="n">
         <v>119672</v>
@@ -45921,6 +45921,32 @@
         <v>709</v>
       </c>
       <c r="H1671" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="1" t="n">
+        <v>45973.6912384259</v>
+      </c>
+      <c r="B1672" t="n">
+        <v>30886</v>
+      </c>
+      <c r="C1672" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="D1672" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="E1672" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="F1672" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="G1672" t="s">
+        <v>708</v>
+      </c>
+      <c r="H1672" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45926,7 +45926,7 @@
     </row>
     <row r="1672">
       <c r="A1672" s="1" t="n">
-        <v>45973.6912384259</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B1672" t="n">
         <v>30886</v>
@@ -45947,6 +45947,32 @@
         <v>708</v>
       </c>
       <c r="H1672" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="1" t="n">
+        <v>45974.6912847222</v>
+      </c>
+      <c r="B1673" t="n">
+        <v>39800</v>
+      </c>
+      <c r="C1673" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="D1673" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1673" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="F1673" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G1673" t="s">
+        <v>697</v>
+      </c>
+      <c r="H1673" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="711">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2142,6 +2142,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.01000022888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9850001335144</t>
   </si>
 </sst>
 </file>
@@ -45952,7 +45955,7 @@
     </row>
     <row r="1673">
       <c r="A1673" s="1" t="n">
-        <v>45974.6912847222</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B1673" t="n">
         <v>39800</v>
@@ -45973,6 +45976,32 @@
         <v>697</v>
       </c>
       <c r="H1673" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="1" t="n">
+        <v>45975.6909953704</v>
+      </c>
+      <c r="B1674" t="n">
+        <v>58432</v>
+      </c>
+      <c r="C1674" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1674" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="E1674" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1674" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="G1674" t="s">
+        <v>710</v>
+      </c>
+      <c r="H1674" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -45981,7 +45981,7 @@
     </row>
     <row r="1674">
       <c r="A1674" s="1" t="n">
-        <v>45975.6909953704</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B1674" t="n">
         <v>58432</v>
@@ -46002,6 +46002,32 @@
         <v>710</v>
       </c>
       <c r="H1674" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="1" t="n">
+        <v>45978.6912962963</v>
+      </c>
+      <c r="B1675" t="n">
+        <v>31364</v>
+      </c>
+      <c r="C1675" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="D1675" t="n">
+        <v>4.94500017166138</v>
+      </c>
+      <c r="E1675" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="F1675" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="G1675" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1675" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46007,7 +46007,7 @@
     </row>
     <row r="1675">
       <c r="A1675" s="1" t="n">
-        <v>45978.6912962963</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B1675" t="n">
         <v>31364</v>
@@ -46028,6 +46028,32 @@
         <v>683</v>
       </c>
       <c r="H1675" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="1" t="n">
+        <v>45979.6911805556</v>
+      </c>
+      <c r="B1676" t="n">
+        <v>58374</v>
+      </c>
+      <c r="C1676" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1676" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="E1676" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="F1676" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1676" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1676" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46033,7 +46033,7 @@
     </row>
     <row r="1676">
       <c r="A1676" s="1" t="n">
-        <v>45979.6911805556</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B1676" t="n">
         <v>58374</v>
@@ -46054,6 +46054,32 @@
         <v>682</v>
       </c>
       <c r="H1676" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="1" t="n">
+        <v>45980.6910763889</v>
+      </c>
+      <c r="B1677" t="n">
+        <v>23877</v>
+      </c>
+      <c r="C1677" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D1677" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="E1677" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="F1677" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="G1677" t="s">
+        <v>710</v>
+      </c>
+      <c r="H1677" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46059,7 +46059,7 @@
     </row>
     <row r="1677">
       <c r="A1677" s="1" t="n">
-        <v>45980.6910763889</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B1677" t="n">
         <v>23877</v>
@@ -46080,6 +46080,32 @@
         <v>710</v>
       </c>
       <c r="H1677" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="1" t="n">
+        <v>45981.6912037037</v>
+      </c>
+      <c r="B1678" t="n">
+        <v>8847</v>
+      </c>
+      <c r="C1678" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="D1678" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1678" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1678" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1678" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1678" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46085,7 +46085,7 @@
     </row>
     <row r="1678">
       <c r="A1678" s="1" t="n">
-        <v>45981.6912037037</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B1678" t="n">
         <v>8847</v>
@@ -46106,6 +46106,32 @@
         <v>682</v>
       </c>
       <c r="H1678" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="1" t="n">
+        <v>45982.69125</v>
+      </c>
+      <c r="B1679" t="n">
+        <v>32160</v>
+      </c>
+      <c r="C1679" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="D1679" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="E1679" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="F1679" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G1679" t="s">
+        <v>697</v>
+      </c>
+      <c r="H1679" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46111,7 +46111,7 @@
     </row>
     <row r="1679">
       <c r="A1679" s="1" t="n">
-        <v>45982.69125</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B1679" t="n">
         <v>32160</v>
@@ -46132,6 +46132,32 @@
         <v>697</v>
       </c>
       <c r="H1679" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="1" t="n">
+        <v>45985.6912731481</v>
+      </c>
+      <c r="B1680" t="n">
+        <v>99975</v>
+      </c>
+      <c r="C1680" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D1680" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="E1680" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="F1680" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1680" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1680" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46137,7 +46137,7 @@
     </row>
     <row r="1680">
       <c r="A1680" s="1" t="n">
-        <v>45985.6912731481</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B1680" t="n">
         <v>99975</v>
@@ -46158,6 +46158,32 @@
         <v>682</v>
       </c>
       <c r="H1680" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="1" t="n">
+        <v>45986.6910416667</v>
+      </c>
+      <c r="B1681" t="n">
+        <v>179775</v>
+      </c>
+      <c r="C1681" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="D1681" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1681" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1681" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1681" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1681" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46163,7 +46163,7 @@
     </row>
     <row r="1681">
       <c r="A1681" s="1" t="n">
-        <v>45986.6910416667</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B1681" t="n">
         <v>179775</v>
@@ -46184,6 +46184,32 @@
         <v>682</v>
       </c>
       <c r="H1681" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="1" t="n">
+        <v>45987.6910069444</v>
+      </c>
+      <c r="B1682" t="n">
+        <v>25841</v>
+      </c>
+      <c r="C1682" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1682" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="E1682" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="F1682" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1682" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1682" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46189,7 +46189,7 @@
     </row>
     <row r="1682">
       <c r="A1682" s="1" t="n">
-        <v>45987.6910069444</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B1682" t="n">
         <v>25841</v>
@@ -46210,6 +46210,32 @@
         <v>682</v>
       </c>
       <c r="H1682" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="1" t="n">
+        <v>45988.6911921296</v>
+      </c>
+      <c r="B1683" t="n">
+        <v>10544</v>
+      </c>
+      <c r="C1683" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="D1683" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="E1683" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="F1683" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="G1683" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1683" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46215,7 +46215,7 @@
     </row>
     <row r="1683">
       <c r="A1683" s="1" t="n">
-        <v>45988.6911921296</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B1683" t="n">
         <v>10544</v>
@@ -46236,6 +46236,32 @@
         <v>683</v>
       </c>
       <c r="H1683" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="1" t="n">
+        <v>45989.6909722222</v>
+      </c>
+      <c r="B1684" t="n">
+        <v>22269</v>
+      </c>
+      <c r="C1684" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1684" t="n">
+        <v>4.97499990463257</v>
+      </c>
+      <c r="E1684" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="F1684" t="n">
+        <v>4.96000003814697</v>
+      </c>
+      <c r="G1684" t="s">
+        <v>680</v>
+      </c>
+      <c r="H1684" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="712">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2145,6 +2145,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.9850001335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97499990463257</t>
   </si>
 </sst>
 </file>
@@ -46241,7 +46244,7 @@
     </row>
     <row r="1684">
       <c r="A1684" s="1" t="n">
-        <v>45989.6909722222</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B1684" t="n">
         <v>22269</v>
@@ -46250,7 +46253,7 @@
         <v>5</v>
       </c>
       <c r="D1684" t="n">
-        <v>4.97499990463257</v>
+        <v>4.96000003814697</v>
       </c>
       <c r="E1684" t="n">
         <v>4.98999977111816</v>
@@ -46262,6 +46265,32 @@
         <v>680</v>
       </c>
       <c r="H1684" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="1" t="n">
+        <v>45992.6909953704</v>
+      </c>
+      <c r="B1685" t="n">
+        <v>28401</v>
+      </c>
+      <c r="C1685" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="D1685" t="n">
+        <v>4.88500022888184</v>
+      </c>
+      <c r="E1685" t="n">
+        <v>4.88500022888184</v>
+      </c>
+      <c r="F1685" t="n">
+        <v>4.97499990463257</v>
+      </c>
+      <c r="G1685" t="s">
+        <v>711</v>
+      </c>
+      <c r="H1685" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46270,7 +46270,7 @@
     </row>
     <row r="1685">
       <c r="A1685" s="1" t="n">
-        <v>45992.6909953704</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B1685" t="n">
         <v>28401</v>
@@ -46291,6 +46291,32 @@
         <v>711</v>
       </c>
       <c r="H1685" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="1" t="n">
+        <v>45993.6910416667</v>
+      </c>
+      <c r="B1686" t="n">
+        <v>36975</v>
+      </c>
+      <c r="C1686" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="D1686" t="n">
+        <v>4.92500019073486</v>
+      </c>
+      <c r="E1686" t="n">
+        <v>4.92500019073486</v>
+      </c>
+      <c r="F1686" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="G1686" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1686" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46296,7 +46296,7 @@
     </row>
     <row r="1686">
       <c r="A1686" s="1" t="n">
-        <v>45993.6910416667</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B1686" t="n">
         <v>36975</v>
@@ -46317,6 +46317,32 @@
         <v>683</v>
       </c>
       <c r="H1686" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="1" t="n">
+        <v>45994.691099537</v>
+      </c>
+      <c r="B1687" t="n">
+        <v>83297</v>
+      </c>
+      <c r="C1687" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="D1687" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="E1687" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="F1687" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="G1687" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1687" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46322,7 +46322,7 @@
     </row>
     <row r="1687">
       <c r="A1687" s="1" t="n">
-        <v>45994.691099537</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B1687" t="n">
         <v>83297</v>
@@ -46343,6 +46343,32 @@
         <v>683</v>
       </c>
       <c r="H1687" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="1" t="n">
+        <v>45995.6910069444</v>
+      </c>
+      <c r="B1688" t="n">
+        <v>69821</v>
+      </c>
+      <c r="C1688" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="D1688" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="E1688" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="F1688" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="G1688" t="s">
+        <v>710</v>
+      </c>
+      <c r="H1688" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46348,7 +46348,7 @@
     </row>
     <row r="1688">
       <c r="A1688" s="1" t="n">
-        <v>45995.6910069444</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B1688" t="n">
         <v>69821</v>
@@ -46369,6 +46369,32 @@
         <v>710</v>
       </c>
       <c r="H1688" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="1" t="n">
+        <v>45996.6911458333</v>
+      </c>
+      <c r="B1689" t="n">
+        <v>29457</v>
+      </c>
+      <c r="C1689" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D1689" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="E1689" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="F1689" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="G1689" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1689" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46374,7 +46374,7 @@
     </row>
     <row r="1689">
       <c r="A1689" s="1" t="n">
-        <v>45996.6911458333</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B1689" t="n">
         <v>29457</v>
@@ -46395,6 +46395,32 @@
         <v>683</v>
       </c>
       <c r="H1689" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="1" t="n">
+        <v>45999.6930439815</v>
+      </c>
+      <c r="B1690" t="n">
+        <v>45101</v>
+      </c>
+      <c r="C1690" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="D1690" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="E1690" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1690" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="G1690" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1690" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46400,7 +46400,7 @@
     </row>
     <row r="1690">
       <c r="A1690" s="1" t="n">
-        <v>45999.6930439815</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B1690" t="n">
         <v>45101</v>
@@ -46421,6 +46421,32 @@
         <v>683</v>
       </c>
       <c r="H1690" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="1" t="n">
+        <v>46000.6912962963</v>
+      </c>
+      <c r="B1691" t="n">
+        <v>64722</v>
+      </c>
+      <c r="C1691" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="D1691" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="E1691" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1691" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="G1691" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1691" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46426,7 +46426,7 @@
     </row>
     <row r="1691">
       <c r="A1691" s="1" t="n">
-        <v>46000.6912962963</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B1691" t="n">
         <v>64722</v>
@@ -46447,6 +46447,32 @@
         <v>683</v>
       </c>
       <c r="H1691" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="1" t="n">
+        <v>46001.6909722222</v>
+      </c>
+      <c r="B1692" t="n">
+        <v>93368</v>
+      </c>
+      <c r="C1692" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1692" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="E1692" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="F1692" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="G1692" t="s">
+        <v>710</v>
+      </c>
+      <c r="H1692" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46452,7 +46452,7 @@
     </row>
     <row r="1692">
       <c r="A1692" s="1" t="n">
-        <v>46001.6909722222</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B1692" t="n">
         <v>93368</v>
@@ -46473,6 +46473,32 @@
         <v>710</v>
       </c>
       <c r="H1692" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="1" t="n">
+        <v>46002.6913078704</v>
+      </c>
+      <c r="B1693" t="n">
+        <v>61270</v>
+      </c>
+      <c r="C1693" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1693" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="E1693" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="F1693" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="G1693" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1693" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46478,7 +46478,7 @@
     </row>
     <row r="1693">
       <c r="A1693" s="1" t="n">
-        <v>46002.6913078704</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B1693" t="n">
         <v>61270</v>
@@ -46499,6 +46499,32 @@
         <v>683</v>
       </c>
       <c r="H1693" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="1" t="n">
+        <v>46003.6909722222</v>
+      </c>
+      <c r="B1694" t="n">
+        <v>66373</v>
+      </c>
+      <c r="C1694" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="D1694" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="E1694" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="F1694" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="G1694" t="s">
+        <v>685</v>
+      </c>
+      <c r="H1694" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46504,7 +46504,7 @@
     </row>
     <row r="1694">
       <c r="A1694" s="1" t="n">
-        <v>46003.6909722222</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B1694" t="n">
         <v>66373</v>
@@ -46525,6 +46525,32 @@
         <v>685</v>
       </c>
       <c r="H1694" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="1" t="n">
+        <v>46006.6912037037</v>
+      </c>
+      <c r="B1695" t="n">
+        <v>50989</v>
+      </c>
+      <c r="C1695" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="D1695" t="n">
+        <v>4.96999979019165</v>
+      </c>
+      <c r="E1695" t="n">
+        <v>4.96999979019165</v>
+      </c>
+      <c r="F1695" t="n">
+        <v>4.96999979019165</v>
+      </c>
+      <c r="G1695" t="s">
+        <v>681</v>
+      </c>
+      <c r="H1695" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46530,7 +46530,7 @@
     </row>
     <row r="1695">
       <c r="A1695" s="1" t="n">
-        <v>46006.6912037037</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B1695" t="n">
         <v>50989</v>
@@ -46551,6 +46551,32 @@
         <v>681</v>
       </c>
       <c r="H1695" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="1" t="n">
+        <v>46007.6910300926</v>
+      </c>
+      <c r="B1696" t="n">
+        <v>54220</v>
+      </c>
+      <c r="C1696" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="D1696" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="E1696" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="F1696" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="G1696" t="s">
+        <v>685</v>
+      </c>
+      <c r="H1696" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46556,7 +46556,7 @@
     </row>
     <row r="1696">
       <c r="A1696" s="1" t="n">
-        <v>46007.6910300926</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B1696" t="n">
         <v>54220</v>
@@ -46577,6 +46577,32 @@
         <v>685</v>
       </c>
       <c r="H1696" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="1" t="n">
+        <v>46008.691099537</v>
+      </c>
+      <c r="B1697" t="n">
+        <v>378414</v>
+      </c>
+      <c r="C1697" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="D1697" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="E1697" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1697" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1697" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1697" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46582,7 +46582,7 @@
     </row>
     <row r="1697">
       <c r="A1697" s="1" t="n">
-        <v>46008.691099537</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B1697" t="n">
         <v>378414</v>
@@ -46603,6 +46603,32 @@
         <v>682</v>
       </c>
       <c r="H1697" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="1" t="n">
+        <v>46009.6909722222</v>
+      </c>
+      <c r="B1698" t="n">
+        <v>160939</v>
+      </c>
+      <c r="C1698" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="D1698" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1698" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1698" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="G1698" t="s">
+        <v>709</v>
+      </c>
+      <c r="H1698" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46608,7 +46608,7 @@
     </row>
     <row r="1698">
       <c r="A1698" s="1" t="n">
-        <v>46009.6909722222</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B1698" t="n">
         <v>160939</v>
@@ -46629,6 +46629,32 @@
         <v>709</v>
       </c>
       <c r="H1698" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="1" t="n">
+        <v>46010.6910069444</v>
+      </c>
+      <c r="B1699" t="n">
+        <v>660516</v>
+      </c>
+      <c r="C1699" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="D1699" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="E1699" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1699" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="G1699" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1699" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46634,7 +46634,7 @@
     </row>
     <row r="1699">
       <c r="A1699" s="1" t="n">
-        <v>46010.6910069444</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B1699" t="n">
         <v>660516</v>
@@ -46655,6 +46655,32 @@
         <v>683</v>
       </c>
       <c r="H1699" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="1" t="n">
+        <v>46013.691087963</v>
+      </c>
+      <c r="B1700" t="n">
+        <v>79762</v>
+      </c>
+      <c r="C1700" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D1700" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="E1700" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="F1700" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G1700" t="s">
+        <v>697</v>
+      </c>
+      <c r="H1700" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46660,7 +46660,7 @@
     </row>
     <row r="1700">
       <c r="A1700" s="1" t="n">
-        <v>46013.691087963</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B1700" t="n">
         <v>79762</v>
@@ -46681,6 +46681,32 @@
         <v>697</v>
       </c>
       <c r="H1700" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="1" t="n">
+        <v>46014.6912962963</v>
+      </c>
+      <c r="B1701" t="n">
+        <v>273480</v>
+      </c>
+      <c r="C1701" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="D1701" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="E1701" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1701" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="G1701" t="s">
+        <v>709</v>
+      </c>
+      <c r="H1701" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46686,7 +46686,7 @@
     </row>
     <row r="1701">
       <c r="A1701" s="1" t="n">
-        <v>46014.6912962963</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B1701" t="n">
         <v>273480</v>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46710,6 +46710,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1702">
+      <c r="A1702" s="1" t="n">
+        <v>46020.6910300926</v>
+      </c>
+      <c r="B1702" t="n">
+        <v>26477</v>
+      </c>
+      <c r="C1702" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D1702" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1702" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1702" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1702" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1702" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46712,7 +46712,7 @@
     </row>
     <row r="1702">
       <c r="A1702" s="1" t="n">
-        <v>46020.6910300926</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B1702" t="n">
         <v>26477</v>
@@ -46733,6 +46733,32 @@
         <v>682</v>
       </c>
       <c r="H1702" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="1" t="n">
+        <v>46021.6912615741</v>
+      </c>
+      <c r="B1703" t="n">
+        <v>35627</v>
+      </c>
+      <c r="C1703" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D1703" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="E1703" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1703" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="G1703" t="s">
+        <v>709</v>
+      </c>
+      <c r="H1703" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46738,7 +46738,7 @@
     </row>
     <row r="1703">
       <c r="A1703" s="1" t="n">
-        <v>46021.6912615741</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B1703" t="n">
         <v>35627</v>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46762,6 +46762,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1704">
+      <c r="A1704" s="1" t="n">
+        <v>46024.6911921296</v>
+      </c>
+      <c r="B1704" t="n">
+        <v>20427</v>
+      </c>
+      <c r="C1704" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="D1704" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1704" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F1704" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="G1704" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1704" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46764,7 +46764,7 @@
     </row>
     <row r="1704">
       <c r="A1704" s="1" t="n">
-        <v>46024.6911921296</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B1704" t="n">
         <v>20427</v>
@@ -46785,6 +46785,32 @@
         <v>698</v>
       </c>
       <c r="H1704" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="1" t="n">
+        <v>46027.6909953704</v>
+      </c>
+      <c r="B1705" t="n">
+        <v>42695</v>
+      </c>
+      <c r="C1705" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="D1705" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="E1705" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="F1705" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G1705" t="s">
+        <v>697</v>
+      </c>
+      <c r="H1705" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46790,7 +46790,7 @@
     </row>
     <row r="1705">
       <c r="A1705" s="1" t="n">
-        <v>46027.6909953704</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B1705" t="n">
         <v>42695</v>
@@ -46811,6 +46811,32 @@
         <v>697</v>
       </c>
       <c r="H1705" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="1" t="n">
+        <v>46028.6449074074</v>
+      </c>
+      <c r="B1706" t="n">
+        <v>3568</v>
+      </c>
+      <c r="C1706" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1706" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="E1706" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1706" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G1706" t="s">
+        <v>697</v>
+      </c>
+      <c r="H1706" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46816,10 +46816,10 @@
     </row>
     <row r="1706">
       <c r="A1706" s="1" t="n">
-        <v>46028.6449074074</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B1706" t="n">
-        <v>3568</v>
+        <v>5590</v>
       </c>
       <c r="C1706" t="n">
         <v>5.03999996185303</v>
@@ -46831,12 +46831,38 @@
         <v>5.01000022888184</v>
       </c>
       <c r="F1706" t="n">
-        <v>5.01999998092651</v>
+        <v>5.01000022888184</v>
       </c>
       <c r="G1706" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="H1706" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="1" t="n">
+        <v>46029.6909837963</v>
+      </c>
+      <c r="B1707" t="n">
+        <v>14408</v>
+      </c>
+      <c r="C1707" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1707" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="E1707" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1707" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="G1707" t="s">
+        <v>708</v>
+      </c>
+      <c r="H1707" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46842,7 +46842,7 @@
     </row>
     <row r="1707">
       <c r="A1707" s="1" t="n">
-        <v>46029.6909837963</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B1707" t="n">
         <v>14408</v>
@@ -46863,6 +46863,32 @@
         <v>708</v>
       </c>
       <c r="H1707" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="1" t="n">
+        <v>46030.6911689815</v>
+      </c>
+      <c r="B1708" t="n">
+        <v>401435</v>
+      </c>
+      <c r="C1708" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="D1708" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="E1708" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="F1708" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="G1708" t="s">
+        <v>686</v>
+      </c>
+      <c r="H1708" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46868,7 +46868,7 @@
     </row>
     <row r="1708">
       <c r="A1708" s="1" t="n">
-        <v>46030.6911689815</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B1708" t="n">
         <v>401435</v>
@@ -46889,6 +46889,32 @@
         <v>686</v>
       </c>
       <c r="H1708" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="1" t="n">
+        <v>46031.6910300926</v>
+      </c>
+      <c r="B1709" t="n">
+        <v>7327</v>
+      </c>
+      <c r="C1709" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D1709" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1709" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1709" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1709" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1709" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46894,7 +46894,7 @@
     </row>
     <row r="1709">
       <c r="A1709" s="1" t="n">
-        <v>46031.6910300926</v>
+        <v>46031.3333333333</v>
       </c>
       <c r="B1709" t="n">
         <v>7327</v>
@@ -46915,6 +46915,32 @@
         <v>682</v>
       </c>
       <c r="H1709" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="1" t="n">
+        <v>46034.6910416667</v>
+      </c>
+      <c r="B1710" t="n">
+        <v>14374</v>
+      </c>
+      <c r="C1710" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1710" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="E1710" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1710" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="G1710" t="s">
+        <v>708</v>
+      </c>
+      <c r="H1710" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46920,7 +46920,7 @@
     </row>
     <row r="1710">
       <c r="A1710" s="1" t="n">
-        <v>46034.6910416667</v>
+        <v>46034.3333333333</v>
       </c>
       <c r="B1710" t="n">
         <v>14374</v>
@@ -46941,6 +46941,32 @@
         <v>708</v>
       </c>
       <c r="H1710" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="1" t="n">
+        <v>46035.6912847222</v>
+      </c>
+      <c r="B1711" t="n">
+        <v>31450</v>
+      </c>
+      <c r="C1711" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1711" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="E1711" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F1711" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="G1711" t="s">
+        <v>709</v>
+      </c>
+      <c r="H1711" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46946,7 +46946,7 @@
     </row>
     <row r="1711">
       <c r="A1711" s="1" t="n">
-        <v>46035.6912847222</v>
+        <v>46035.3333333333</v>
       </c>
       <c r="B1711" t="n">
         <v>31450</v>
@@ -46967,6 +46967,32 @@
         <v>709</v>
       </c>
       <c r="H1711" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="1" t="n">
+        <v>46036.6911574074</v>
+      </c>
+      <c r="B1712" t="n">
+        <v>20879</v>
+      </c>
+      <c r="C1712" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="D1712" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1712" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1712" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1712" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1712" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46972,7 +46972,7 @@
     </row>
     <row r="1712">
       <c r="A1712" s="1" t="n">
-        <v>46036.6911574074</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B1712" t="n">
         <v>20879</v>
@@ -46993,6 +46993,32 @@
         <v>682</v>
       </c>
       <c r="H1712" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="1" t="n">
+        <v>46037.6912847222</v>
+      </c>
+      <c r="B1713" t="n">
+        <v>478801</v>
+      </c>
+      <c r="C1713" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="D1713" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1713" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1713" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G1713" t="s">
+        <v>697</v>
+      </c>
+      <c r="H1713" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -46998,13 +46998,13 @@
     </row>
     <row r="1713">
       <c r="A1713" s="1" t="n">
-        <v>46037.6912847222</v>
+        <v>46037.3333333333</v>
       </c>
       <c r="B1713" t="n">
         <v>478801</v>
       </c>
       <c r="C1713" t="n">
-        <v>5.01000022888184</v>
+        <v>5.01999998092651</v>
       </c>
       <c r="D1713" t="n">
         <v>5</v>
@@ -47019,6 +47019,32 @@
         <v>697</v>
       </c>
       <c r="H1713" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="1" t="n">
+        <v>46038.6912615741</v>
+      </c>
+      <c r="B1714" t="n">
+        <v>124759</v>
+      </c>
+      <c r="C1714" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1714" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1714" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1714" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="G1714" t="s">
+        <v>708</v>
+      </c>
+      <c r="H1714" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47024,7 +47024,7 @@
     </row>
     <row r="1714">
       <c r="A1714" s="1" t="n">
-        <v>46038.6912615741</v>
+        <v>46038.3333333333</v>
       </c>
       <c r="B1714" t="n">
         <v>124759</v>
@@ -47045,6 +47045,32 @@
         <v>708</v>
       </c>
       <c r="H1714" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="1" t="n">
+        <v>46041.6912384259</v>
+      </c>
+      <c r="B1715" t="n">
+        <v>52670</v>
+      </c>
+      <c r="C1715" t="n">
+        <v>5.15000009536743</v>
+      </c>
+      <c r="D1715" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="E1715" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="F1715" t="n">
+        <v>5.15000009536743</v>
+      </c>
+      <c r="G1715" t="s">
+        <v>705</v>
+      </c>
+      <c r="H1715" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47050,7 +47050,7 @@
     </row>
     <row r="1715">
       <c r="A1715" s="1" t="n">
-        <v>46041.6912384259</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B1715" t="n">
         <v>52670</v>
@@ -47071,6 +47071,32 @@
         <v>705</v>
       </c>
       <c r="H1715" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="1" t="n">
+        <v>46042.691099537</v>
+      </c>
+      <c r="B1716" t="n">
+        <v>38121</v>
+      </c>
+      <c r="C1716" t="n">
+        <v>5.15999984741211</v>
+      </c>
+      <c r="D1716" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="E1716" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="F1716" t="n">
+        <v>5.13000011444092</v>
+      </c>
+      <c r="G1716" t="s">
+        <v>704</v>
+      </c>
+      <c r="H1716" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47076,7 +47076,7 @@
     </row>
     <row r="1716">
       <c r="A1716" s="1" t="n">
-        <v>46042.691099537</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B1716" t="n">
         <v>38121</v>
@@ -47097,6 +47097,32 @@
         <v>704</v>
       </c>
       <c r="H1716" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="1" t="n">
+        <v>46043.6928240741</v>
+      </c>
+      <c r="B1717" t="n">
+        <v>49214</v>
+      </c>
+      <c r="C1717" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="D1717" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="E1717" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="F1717" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="G1717" t="s">
+        <v>702</v>
+      </c>
+      <c r="H1717" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47102,7 +47102,7 @@
     </row>
     <row r="1717">
       <c r="A1717" s="1" t="n">
-        <v>46043.6928240741</v>
+        <v>46043.3333333333</v>
       </c>
       <c r="B1717" t="n">
         <v>49214</v>
@@ -47123,6 +47123,32 @@
         <v>702</v>
       </c>
       <c r="H1717" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="1" t="n">
+        <v>46044.691087963</v>
+      </c>
+      <c r="B1718" t="n">
+        <v>242188</v>
+      </c>
+      <c r="C1718" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="D1718" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="E1718" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="F1718" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1718" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1718" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47128,7 +47128,7 @@
     </row>
     <row r="1718">
       <c r="A1718" s="1" t="n">
-        <v>46044.691087963</v>
+        <v>46044.3333333333</v>
       </c>
       <c r="B1718" t="n">
         <v>242188</v>
@@ -47149,6 +47149,32 @@
         <v>700</v>
       </c>
       <c r="H1718" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="1" t="n">
+        <v>46045.6912615741</v>
+      </c>
+      <c r="B1719" t="n">
+        <v>71272</v>
+      </c>
+      <c r="C1719" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="D1719" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E1719" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="F1719" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="G1719" t="s">
+        <v>699</v>
+      </c>
+      <c r="H1719" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47154,7 +47154,7 @@
     </row>
     <row r="1719">
       <c r="A1719" s="1" t="n">
-        <v>46045.6912615741</v>
+        <v>46045.3333333333</v>
       </c>
       <c r="B1719" t="n">
         <v>71272</v>
@@ -47175,6 +47175,32 @@
         <v>699</v>
       </c>
       <c r="H1719" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="1" t="n">
+        <v>46048.6910648148</v>
+      </c>
+      <c r="B1720" t="n">
+        <v>244262</v>
+      </c>
+      <c r="C1720" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="D1720" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="E1720" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="F1720" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="G1720" t="s">
+        <v>702</v>
+      </c>
+      <c r="H1720" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="713">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2148,6 +2148,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.97499990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07000017166138</t>
   </si>
 </sst>
 </file>
@@ -47180,7 +47183,7 @@
     </row>
     <row r="1720">
       <c r="A1720" s="1" t="n">
-        <v>46048.6910648148</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B1720" t="n">
         <v>244262</v>
@@ -47201,6 +47204,32 @@
         <v>702</v>
       </c>
       <c r="H1720" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="1" t="n">
+        <v>46049.691087963</v>
+      </c>
+      <c r="B1721" t="n">
+        <v>290496</v>
+      </c>
+      <c r="C1721" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="D1721" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E1721" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="F1721" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="G1721" t="s">
+        <v>712</v>
+      </c>
+      <c r="H1721" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47209,7 +47209,7 @@
     </row>
     <row r="1721">
       <c r="A1721" s="1" t="n">
-        <v>46049.691087963</v>
+        <v>46049.3333333333</v>
       </c>
       <c r="B1721" t="n">
         <v>290496</v>
@@ -47230,6 +47230,32 @@
         <v>712</v>
       </c>
       <c r="H1721" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="1" t="n">
+        <v>46050.6910532407</v>
+      </c>
+      <c r="B1722" t="n">
+        <v>104606</v>
+      </c>
+      <c r="C1722" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="D1722" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="E1722" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="F1722" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1722" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1722" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47235,7 +47235,7 @@
     </row>
     <row r="1722">
       <c r="A1722" s="1" t="n">
-        <v>46050.6910532407</v>
+        <v>46050.3333333333</v>
       </c>
       <c r="B1722" t="n">
         <v>104606</v>
@@ -47244,7 +47244,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="D1722" t="n">
-        <v>5.05999994277954</v>
+        <v>5.05000019073486</v>
       </c>
       <c r="E1722" t="n">
         <v>5.05999994277954</v>
@@ -47256,6 +47256,32 @@
         <v>700</v>
       </c>
       <c r="H1722" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="1" t="n">
+        <v>46051.6909837963</v>
+      </c>
+      <c r="B1723" t="n">
+        <v>12269</v>
+      </c>
+      <c r="C1723" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="D1723" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E1723" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1723" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1723" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1723" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47261,7 +47261,7 @@
     </row>
     <row r="1723">
       <c r="A1723" s="1" t="n">
-        <v>46051.6909837963</v>
+        <v>46051.3333333333</v>
       </c>
       <c r="B1723" t="n">
         <v>12269</v>
@@ -47282,6 +47282,32 @@
         <v>700</v>
       </c>
       <c r="H1723" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="1" t="n">
+        <v>46052.6936574074</v>
+      </c>
+      <c r="B1724" t="n">
+        <v>190800</v>
+      </c>
+      <c r="C1724" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="D1724" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="E1724" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="F1724" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="G1724" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1724" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47287,7 +47287,7 @@
     </row>
     <row r="1724">
       <c r="A1724" s="1" t="n">
-        <v>46052.6936574074</v>
+        <v>46052.3333333333</v>
       </c>
       <c r="B1724" t="n">
         <v>190800</v>
@@ -47308,6 +47308,32 @@
         <v>698</v>
       </c>
       <c r="H1724" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="1" t="n">
+        <v>46055.6910416667</v>
+      </c>
+      <c r="B1725" t="n">
+        <v>137947</v>
+      </c>
+      <c r="C1725" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="D1725" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="E1725" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1725" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="G1725" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1725" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47313,7 +47313,7 @@
     </row>
     <row r="1725">
       <c r="A1725" s="1" t="n">
-        <v>46055.6910416667</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B1725" t="n">
         <v>137947</v>
@@ -47334,6 +47334,32 @@
         <v>698</v>
       </c>
       <c r="H1725" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="1" t="n">
+        <v>46056.6910185185</v>
+      </c>
+      <c r="B1726" t="n">
+        <v>293812</v>
+      </c>
+      <c r="C1726" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="D1726" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="E1726" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="F1726" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="G1726" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1726" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47339,7 +47339,7 @@
     </row>
     <row r="1726">
       <c r="A1726" s="1" t="n">
-        <v>46056.6910185185</v>
+        <v>46056.3333333333</v>
       </c>
       <c r="B1726" t="n">
         <v>293812</v>
@@ -47351,7 +47351,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="E1726" t="n">
-        <v>5.09000015258789</v>
+        <v>5.05000019073486</v>
       </c>
       <c r="F1726" t="n">
         <v>5.03999996185303</v>
@@ -47360,6 +47360,32 @@
         <v>698</v>
       </c>
       <c r="H1726" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="1" t="n">
+        <v>46057.6911226852</v>
+      </c>
+      <c r="B1727" t="n">
+        <v>767963</v>
+      </c>
+      <c r="C1727" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="D1727" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="E1727" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F1727" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1727" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1727" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47365,7 +47365,7 @@
     </row>
     <row r="1727">
       <c r="A1727" s="1" t="n">
-        <v>46057.6911226852</v>
+        <v>46057.3333333333</v>
       </c>
       <c r="B1727" t="n">
         <v>767963</v>
@@ -47386,6 +47386,32 @@
         <v>700</v>
       </c>
       <c r="H1727" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="1" t="n">
+        <v>46058.6910763889</v>
+      </c>
+      <c r="B1728" t="n">
+        <v>207427</v>
+      </c>
+      <c r="C1728" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="D1728" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E1728" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1728" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1728" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1728" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47391,7 +47391,7 @@
     </row>
     <row r="1728">
       <c r="A1728" s="1" t="n">
-        <v>46058.6910763889</v>
+        <v>46058.3333333333</v>
       </c>
       <c r="B1728" t="n">
         <v>207427</v>
@@ -47412,6 +47412,32 @@
         <v>700</v>
       </c>
       <c r="H1728" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="1" t="n">
+        <v>46059.6912037037</v>
+      </c>
+      <c r="B1729" t="n">
+        <v>79039</v>
+      </c>
+      <c r="C1729" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="D1729" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E1729" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1729" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="G1729" t="s">
+        <v>699</v>
+      </c>
+      <c r="H1729" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47417,7 +47417,7 @@
     </row>
     <row r="1729">
       <c r="A1729" s="1" t="n">
-        <v>46059.6912037037</v>
+        <v>46059.3333333333</v>
       </c>
       <c r="B1729" t="n">
         <v>79039</v>
@@ -47438,6 +47438,32 @@
         <v>699</v>
       </c>
       <c r="H1729" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="1" t="n">
+        <v>46062.6912615741</v>
+      </c>
+      <c r="B1730" t="n">
+        <v>29237</v>
+      </c>
+      <c r="C1730" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="D1730" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="E1730" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="F1730" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="G1730" t="s">
+        <v>702</v>
+      </c>
+      <c r="H1730" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47443,7 +47443,7 @@
     </row>
     <row r="1730">
       <c r="A1730" s="1" t="n">
-        <v>46062.6912615741</v>
+        <v>46062.3333333333</v>
       </c>
       <c r="B1730" t="n">
         <v>29237</v>
@@ -47464,6 +47464,32 @@
         <v>702</v>
       </c>
       <c r="H1730" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="1" t="n">
+        <v>46063.6912615741</v>
+      </c>
+      <c r="B1731" t="n">
+        <v>39884</v>
+      </c>
+      <c r="C1731" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="D1731" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="E1731" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="F1731" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="G1731" t="s">
+        <v>702</v>
+      </c>
+      <c r="H1731" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47469,13 +47469,13 @@
     </row>
     <row r="1731">
       <c r="A1731" s="1" t="n">
-        <v>46063.6912615741</v>
+        <v>46063.3333333333</v>
       </c>
       <c r="B1731" t="n">
         <v>39884</v>
       </c>
       <c r="C1731" t="n">
-        <v>5.09000015258789</v>
+        <v>5.09999990463257</v>
       </c>
       <c r="D1731" t="n">
         <v>5.05999994277954</v>
@@ -47490,6 +47490,32 @@
         <v>702</v>
       </c>
       <c r="H1731" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="1" t="n">
+        <v>46064.6911689815</v>
+      </c>
+      <c r="B1732" t="n">
+        <v>21832</v>
+      </c>
+      <c r="C1732" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="D1732" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="E1732" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="F1732" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="G1732" t="s">
+        <v>701</v>
+      </c>
+      <c r="H1732" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47495,7 +47495,7 @@
     </row>
     <row r="1732">
       <c r="A1732" s="1" t="n">
-        <v>46064.6911689815</v>
+        <v>46064.3333333333</v>
       </c>
       <c r="B1732" t="n">
         <v>21832</v>
@@ -47516,6 +47516,32 @@
         <v>701</v>
       </c>
       <c r="H1732" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="1" t="n">
+        <v>46065.6912615741</v>
+      </c>
+      <c r="B1733" t="n">
+        <v>51788</v>
+      </c>
+      <c r="C1733" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="D1733" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E1733" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="F1733" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1733" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1733" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47521,7 +47521,7 @@
     </row>
     <row r="1733">
       <c r="A1733" s="1" t="n">
-        <v>46065.6912615741</v>
+        <v>46065.3333333333</v>
       </c>
       <c r="B1733" t="n">
         <v>51788</v>
@@ -47542,6 +47542,32 @@
         <v>700</v>
       </c>
       <c r="H1733" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="1" t="n">
+        <v>46066.6913078704</v>
+      </c>
+      <c r="B1734" t="n">
+        <v>60292</v>
+      </c>
+      <c r="C1734" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="D1734" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E1734" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1734" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1734" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1734" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47547,7 +47547,7 @@
     </row>
     <row r="1734">
       <c r="A1734" s="1" t="n">
-        <v>46066.6913078704</v>
+        <v>46066.3333333333</v>
       </c>
       <c r="B1734" t="n">
         <v>60292</v>
@@ -47568,6 +47568,32 @@
         <v>700</v>
       </c>
       <c r="H1734" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="1" t="n">
+        <v>46069.6942476852</v>
+      </c>
+      <c r="B1735" t="n">
+        <v>166900</v>
+      </c>
+      <c r="C1735" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="D1735" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="E1735" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1735" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="G1735" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1735" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47573,7 +47573,7 @@
     </row>
     <row r="1735">
       <c r="A1735" s="1" t="n">
-        <v>46069.6942476852</v>
+        <v>46069.3333333333</v>
       </c>
       <c r="B1735" t="n">
         <v>166900</v>
@@ -47594,6 +47594,32 @@
         <v>698</v>
       </c>
       <c r="H1735" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="1" t="n">
+        <v>46070.69125</v>
+      </c>
+      <c r="B1736" t="n">
+        <v>70550</v>
+      </c>
+      <c r="C1736" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1736" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1736" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="F1736" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="G1736" t="s">
+        <v>709</v>
+      </c>
+      <c r="H1736" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47599,7 +47599,7 @@
     </row>
     <row r="1736">
       <c r="A1736" s="1" t="n">
-        <v>46070.69125</v>
+        <v>46070.3333333333</v>
       </c>
       <c r="B1736" t="n">
         <v>70550</v>
@@ -47620,6 +47620,32 @@
         <v>709</v>
       </c>
       <c r="H1736" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="1" t="n">
+        <v>46071.6912962963</v>
+      </c>
+      <c r="B1737" t="n">
+        <v>61357</v>
+      </c>
+      <c r="C1737" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="D1737" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1737" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1737" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47625,7 +47625,7 @@
     </row>
     <row r="1737">
       <c r="A1737" s="1" t="n">
-        <v>46071.6912962963</v>
+        <v>46071.3333333333</v>
       </c>
       <c r="B1737" t="n">
         <v>61357</v>
@@ -47646,6 +47646,32 @@
         <v>682</v>
       </c>
       <c r="H1737" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="1" t="n">
+        <v>46072.6920138889</v>
+      </c>
+      <c r="B1738" t="n">
+        <v>113020</v>
+      </c>
+      <c r="C1738" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D1738" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1738" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1738" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="G1738" t="s">
+        <v>708</v>
+      </c>
+      <c r="H1738" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47651,13 +47651,13 @@
     </row>
     <row r="1738">
       <c r="A1738" s="1" t="n">
-        <v>46072.6920138889</v>
+        <v>46072.3333333333</v>
       </c>
       <c r="B1738" t="n">
         <v>113020</v>
       </c>
       <c r="C1738" t="n">
-        <v>5.01999998092651</v>
+        <v>5.03000020980835</v>
       </c>
       <c r="D1738" t="n">
         <v>5</v>
@@ -47672,6 +47672,32 @@
         <v>708</v>
       </c>
       <c r="H1738" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="1" t="n">
+        <v>46073.6910416667</v>
+      </c>
+      <c r="B1739" t="n">
+        <v>65234</v>
+      </c>
+      <c r="C1739" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="D1739" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1739" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1739" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="G1739" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1739" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47677,13 +47677,13 @@
     </row>
     <row r="1739">
       <c r="A1739" s="1" t="n">
-        <v>46073.6910416667</v>
+        <v>46073.3333333333</v>
       </c>
       <c r="B1739" t="n">
         <v>65234</v>
       </c>
       <c r="C1739" t="n">
-        <v>5.03000020980835</v>
+        <v>5.03999996185303</v>
       </c>
       <c r="D1739" t="n">
         <v>5</v>
@@ -47698,6 +47698,32 @@
         <v>698</v>
       </c>
       <c r="H1739" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="1" t="n">
+        <v>46076.6909837963</v>
+      </c>
+      <c r="B1740" t="n">
+        <v>64836</v>
+      </c>
+      <c r="C1740" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="D1740" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1740" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1740" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1740" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1740" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47703,7 +47703,7 @@
     </row>
     <row r="1740">
       <c r="A1740" s="1" t="n">
-        <v>46076.6909837963</v>
+        <v>46076.3333333333</v>
       </c>
       <c r="B1740" t="n">
         <v>64836</v>
@@ -47724,6 +47724,32 @@
         <v>700</v>
       </c>
       <c r="H1740" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="1" t="n">
+        <v>46077.691099537</v>
+      </c>
+      <c r="B1741" t="n">
+        <v>112154</v>
+      </c>
+      <c r="C1741" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="D1741" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1741" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1741" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="G1741" t="s">
+        <v>699</v>
+      </c>
+      <c r="H1741" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47729,7 +47729,7 @@
     </row>
     <row r="1741">
       <c r="A1741" s="1" t="n">
-        <v>46077.691099537</v>
+        <v>46077.3333333333</v>
       </c>
       <c r="B1741" t="n">
         <v>112154</v>
@@ -47750,6 +47750,32 @@
         <v>699</v>
       </c>
       <c r="H1741" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="1" t="n">
+        <v>46078.6910763889</v>
+      </c>
+      <c r="B1742" t="n">
+        <v>27991</v>
+      </c>
+      <c r="C1742" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="D1742" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="G1742" t="s">
+        <v>699</v>
+      </c>
+      <c r="H1742" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47755,7 +47755,7 @@
     </row>
     <row r="1742">
       <c r="A1742" s="1" t="n">
-        <v>46078.6910763889</v>
+        <v>46078.3333333333</v>
       </c>
       <c r="B1742" t="n">
         <v>27991</v>
@@ -47776,6 +47776,32 @@
         <v>699</v>
       </c>
       <c r="H1742" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="1" t="n">
+        <v>46079.6910532407</v>
+      </c>
+      <c r="B1743" t="n">
+        <v>49694</v>
+      </c>
+      <c r="C1743" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="D1743" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E1743" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1743" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1743" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1743" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47781,7 +47781,7 @@
     </row>
     <row r="1743">
       <c r="A1743" s="1" t="n">
-        <v>46079.6910532407</v>
+        <v>46079.3333333333</v>
       </c>
       <c r="B1743" t="n">
         <v>49694</v>
@@ -47802,6 +47802,32 @@
         <v>700</v>
       </c>
       <c r="H1743" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="1" t="n">
+        <v>46080.6910416667</v>
+      </c>
+      <c r="B1744" t="n">
+        <v>34875</v>
+      </c>
+      <c r="C1744" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="D1744" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E1744" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1744" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="G1744" t="s">
+        <v>699</v>
+      </c>
+      <c r="H1744" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47807,7 +47807,7 @@
     </row>
     <row r="1744">
       <c r="A1744" s="1" t="n">
-        <v>46080.6910416667</v>
+        <v>46080.3333333333</v>
       </c>
       <c r="B1744" t="n">
         <v>34875</v>
@@ -47828,6 +47828,32 @@
         <v>699</v>
       </c>
       <c r="H1744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="1" t="n">
+        <v>46083.6911805556</v>
+      </c>
+      <c r="B1745" t="n">
+        <v>31142</v>
+      </c>
+      <c r="C1745" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1745" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1745" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1745" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="G1745" t="s">
+        <v>708</v>
+      </c>
+      <c r="H1745" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47833,7 +47833,7 @@
     </row>
     <row r="1745">
       <c r="A1745" s="1" t="n">
-        <v>46083.6911805556</v>
+        <v>46083.3333333333</v>
       </c>
       <c r="B1745" t="n">
         <v>31142</v>
@@ -47854,6 +47854,32 @@
         <v>708</v>
       </c>
       <c r="H1745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="1" t="n">
+        <v>46084.6910185185</v>
+      </c>
+      <c r="B1746" t="n">
+        <v>39158</v>
+      </c>
+      <c r="C1746" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1746" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1746" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1746" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G1746" t="s">
+        <v>697</v>
+      </c>
+      <c r="H1746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47859,7 +47859,7 @@
     </row>
     <row r="1746">
       <c r="A1746" s="1" t="n">
-        <v>46084.6910185185</v>
+        <v>46084.3333333333</v>
       </c>
       <c r="B1746" t="n">
         <v>39158</v>
@@ -47880,6 +47880,32 @@
         <v>697</v>
       </c>
       <c r="H1746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="1" t="n">
+        <v>46085.6909722222</v>
+      </c>
+      <c r="B1747" t="n">
+        <v>285284</v>
+      </c>
+      <c r="C1747" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="D1747" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="E1747" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1747" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="G1747" t="s">
+        <v>708</v>
+      </c>
+      <c r="H1747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47885,7 +47885,7 @@
     </row>
     <row r="1747">
       <c r="A1747" s="1" t="n">
-        <v>46085.6909722222</v>
+        <v>46085.3333333333</v>
       </c>
       <c r="B1747" t="n">
         <v>285284</v>
@@ -47906,6 +47906,32 @@
         <v>708</v>
       </c>
       <c r="H1747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="1" t="n">
+        <v>46086.6911342593</v>
+      </c>
+      <c r="B1748" t="n">
+        <v>65898</v>
+      </c>
+      <c r="C1748" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1748" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="F1748" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="G1748" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47911,7 +47911,7 @@
     </row>
     <row r="1748">
       <c r="A1748" s="1" t="n">
-        <v>46086.6911342593</v>
+        <v>46086.3333333333</v>
       </c>
       <c r="B1748" t="n">
         <v>65898</v>
@@ -47932,6 +47932,32 @@
         <v>698</v>
       </c>
       <c r="H1748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="1" t="n">
+        <v>46087.6909953704</v>
+      </c>
+      <c r="B1749" t="n">
+        <v>121592</v>
+      </c>
+      <c r="C1749" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="D1749" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1749" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G1749" t="s">
+        <v>697</v>
+      </c>
+      <c r="H1749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47937,7 +47937,7 @@
     </row>
     <row r="1749">
       <c r="A1749" s="1" t="n">
-        <v>46087.6909953704</v>
+        <v>46087.3333333333</v>
       </c>
       <c r="B1749" t="n">
         <v>121592</v>
@@ -47958,6 +47958,32 @@
         <v>697</v>
       </c>
       <c r="H1749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="1" t="n">
+        <v>46090.6912962963</v>
+      </c>
+      <c r="B1750" t="n">
+        <v>53909</v>
+      </c>
+      <c r="C1750" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D1750" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1750" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47963,7 +47963,7 @@
     </row>
     <row r="1750">
       <c r="A1750" s="1" t="n">
-        <v>46090.6912962963</v>
+        <v>46090.3333333333</v>
       </c>
       <c r="B1750" t="n">
         <v>53909</v>
@@ -47984,6 +47984,32 @@
         <v>682</v>
       </c>
       <c r="H1750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="1" t="n">
+        <v>46091.6911805556</v>
+      </c>
+      <c r="B1751" t="n">
+        <v>101168</v>
+      </c>
+      <c r="C1751" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G1751" t="s">
+        <v>697</v>
+      </c>
+      <c r="H1751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -47989,7 +47989,7 @@
     </row>
     <row r="1751">
       <c r="A1751" s="1" t="n">
-        <v>46091.6911805556</v>
+        <v>46091.3333333333</v>
       </c>
       <c r="B1751" t="n">
         <v>101168</v>
@@ -48010,6 +48010,32 @@
         <v>697</v>
       </c>
       <c r="H1751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="1" t="n">
+        <v>46092.6913078704</v>
+      </c>
+      <c r="B1752" t="n">
+        <v>30592</v>
+      </c>
+      <c r="C1752" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="D1752" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1752" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1752" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="G1752" t="s">
+        <v>708</v>
+      </c>
+      <c r="H1752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -48015,7 +48015,7 @@
     </row>
     <row r="1752">
       <c r="A1752" s="1" t="n">
-        <v>46092.6913078704</v>
+        <v>46092.3333333333</v>
       </c>
       <c r="B1752" t="n">
         <v>30592</v>
@@ -48036,6 +48036,32 @@
         <v>708</v>
       </c>
       <c r="H1752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="1" t="n">
+        <v>46093.6919328704</v>
+      </c>
+      <c r="B1753" t="n">
+        <v>44745</v>
+      </c>
+      <c r="C1753" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="D1753" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1753" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F1753" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G1753" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="714">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2151,6 +2151,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.07000017166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -48041,7 +48044,7 @@
     </row>
     <row r="1753">
       <c r="A1753" s="1" t="n">
-        <v>46093.6919328704</v>
+        <v>46093.3333333333</v>
       </c>
       <c r="B1753" t="n">
         <v>44745</v>
@@ -48062,6 +48065,56 @@
         <v>700</v>
       </c>
       <c r="H1753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="1" t="n">
+        <v>46094.3333333333</v>
+      </c>
+      <c r="B1754" t="n">
+        <v>59504</v>
+      </c>
+      <c r="C1754" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="D1754" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="E1754" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1754"/>
+      <c r="G1754" t="s">
+        <v>713</v>
+      </c>
+      <c r="H1754" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="1" t="n">
+        <v>46094.6911689815</v>
+      </c>
+      <c r="B1755" t="n">
+        <v>59504</v>
+      </c>
+      <c r="C1755" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="D1755" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="E1755" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F1755" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G1755" t="s">
+        <v>697</v>
+      </c>
+      <c r="H1755" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -48079,14 +48079,16 @@
         <v>5.05000019073486</v>
       </c>
       <c r="D1754" t="n">
-        <v>5.03000020980835</v>
+        <v>5.01999998092651</v>
       </c>
       <c r="E1754" t="n">
         <v>5.05000019073486</v>
       </c>
-      <c r="F1754"/>
+      <c r="F1754" t="n">
+        <v>5.01999998092651</v>
+      </c>
       <c r="G1754" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48094,27 +48096,51 @@
     </row>
     <row r="1755">
       <c r="A1755" s="1" t="n">
-        <v>46094.6911689815</v>
+        <v>46097.3333333333</v>
       </c>
       <c r="B1755" t="n">
-        <v>59504</v>
+        <v>92646</v>
       </c>
       <c r="C1755" t="n">
-        <v>5.05000019073486</v>
+        <v>5.03999996185303</v>
       </c>
       <c r="D1755" t="n">
-        <v>5.03000020980835</v>
+        <v>5.01999998092651</v>
       </c>
       <c r="E1755" t="n">
-        <v>5.05000019073486</v>
-      </c>
-      <c r="F1755" t="n">
         <v>5.01999998092651</v>
       </c>
+      <c r="F1755"/>
       <c r="G1755" t="s">
+        <v>713</v>
+      </c>
+      <c r="H1755" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="1" t="n">
+        <v>46097.6911574074</v>
+      </c>
+      <c r="B1756" t="n">
+        <v>92646</v>
+      </c>
+      <c r="C1756" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1756" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1756" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1756" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G1756" t="s">
         <v>697</v>
       </c>
-      <c r="H1755" t="s">
+      <c r="H1756" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -48110,9 +48110,11 @@
       <c r="E1755" t="n">
         <v>5.01999998092651</v>
       </c>
-      <c r="F1755"/>
+      <c r="F1755" t="n">
+        <v>5.01999998092651</v>
+      </c>
       <c r="G1755" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48120,27 +48122,51 @@
     </row>
     <row r="1756">
       <c r="A1756" s="1" t="n">
-        <v>46097.6911574074</v>
+        <v>46098.3333333333</v>
       </c>
       <c r="B1756" t="n">
-        <v>92646</v>
+        <v>46340</v>
       </c>
       <c r="C1756" t="n">
-        <v>5.03999996185303</v>
+        <v>5</v>
       </c>
       <c r="D1756" t="n">
-        <v>5.01999998092651</v>
+        <v>4.98999977111816</v>
       </c>
       <c r="E1756" t="n">
-        <v>5.01999998092651</v>
-      </c>
-      <c r="F1756" t="n">
-        <v>5.01999998092651</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F1756"/>
       <c r="G1756" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
       <c r="H1756" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="1" t="n">
+        <v>46098.6912037037</v>
+      </c>
+      <c r="B1757" t="n">
+        <v>46340</v>
+      </c>
+      <c r="C1757" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1757" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="G1757" t="s">
+        <v>686</v>
+      </c>
+      <c r="H1757" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -48136,9 +48136,11 @@
       <c r="E1756" t="n">
         <v>5</v>
       </c>
-      <c r="F1756"/>
+      <c r="F1756" t="n">
+        <v>4.99499988555908</v>
+      </c>
       <c r="G1756" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48146,27 +48148,51 @@
     </row>
     <row r="1757">
       <c r="A1757" s="1" t="n">
-        <v>46098.6912037037</v>
+        <v>46099.3333333333</v>
       </c>
       <c r="B1757" t="n">
-        <v>46340</v>
+        <v>803313</v>
       </c>
       <c r="C1757" t="n">
-        <v>5</v>
+        <v>4.99499988555908</v>
       </c>
       <c r="D1757" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="F1757"/>
+      <c r="G1757" t="s">
+        <v>713</v>
+      </c>
+      <c r="H1757" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="1" t="n">
+        <v>46099.6911574074</v>
+      </c>
+      <c r="B1758" t="n">
+        <v>803313</v>
+      </c>
+      <c r="C1758" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="D1758" t="n">
+        <v>4.9850001335144</v>
+      </c>
+      <c r="E1758" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="F1758" t="n">
         <v>4.98999977111816</v>
       </c>
-      <c r="E1757" t="n">
-        <v>5</v>
-      </c>
-      <c r="F1757" t="n">
-        <v>4.99499988555908</v>
-      </c>
-      <c r="G1757" t="s">
-        <v>686</v>
-      </c>
-      <c r="H1757" t="s">
+      <c r="G1758" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1758" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -48162,9 +48162,11 @@
       <c r="E1757" t="n">
         <v>4.99499988555908</v>
       </c>
-      <c r="F1757"/>
+      <c r="F1757" t="n">
+        <v>4.98999977111816</v>
+      </c>
       <c r="G1757" t="s">
-        <v>713</v>
+        <v>683</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48172,27 +48174,51 @@
     </row>
     <row r="1758">
       <c r="A1758" s="1" t="n">
-        <v>46099.6911574074</v>
+        <v>46100.3333333333</v>
       </c>
       <c r="B1758" t="n">
-        <v>803313</v>
+        <v>71743</v>
       </c>
       <c r="C1758" t="n">
-        <v>4.99499988555908</v>
+        <v>4.98000001907349</v>
       </c>
       <c r="D1758" t="n">
-        <v>4.9850001335144</v>
+        <v>4.82000017166138</v>
       </c>
       <c r="E1758" t="n">
-        <v>4.99499988555908</v>
-      </c>
-      <c r="F1758" t="n">
-        <v>4.98999977111816</v>
-      </c>
+        <v>4.92500019073486</v>
+      </c>
+      <c r="F1758"/>
       <c r="G1758" t="s">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="H1758" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="1" t="n">
+        <v>46100.69125</v>
+      </c>
+      <c r="B1759" t="n">
+        <v>71743</v>
+      </c>
+      <c r="C1759" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="D1759" t="n">
+        <v>4.82000017166138</v>
+      </c>
+      <c r="E1759" t="n">
+        <v>4.92500019073486</v>
+      </c>
+      <c r="F1759" t="n">
+        <v>4.94999980926514</v>
+      </c>
+      <c r="G1759" t="s">
+        <v>684</v>
+      </c>
+      <c r="H1759" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -48188,9 +48188,11 @@
       <c r="E1758" t="n">
         <v>4.92500019073486</v>
       </c>
-      <c r="F1758"/>
+      <c r="F1758" t="n">
+        <v>4.94999980926514</v>
+      </c>
       <c r="G1758" t="s">
-        <v>713</v>
+        <v>684</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48198,27 +48200,51 @@
     </row>
     <row r="1759">
       <c r="A1759" s="1" t="n">
-        <v>46100.69125</v>
+        <v>46101.3333333333</v>
       </c>
       <c r="B1759" t="n">
-        <v>71743</v>
+        <v>4559253</v>
       </c>
       <c r="C1759" t="n">
-        <v>4.98000001907349</v>
+        <v>5.01999998092651</v>
       </c>
       <c r="D1759" t="n">
-        <v>4.82000017166138</v>
+        <v>4.95499992370605</v>
       </c>
       <c r="E1759" t="n">
-        <v>4.92500019073486</v>
-      </c>
-      <c r="F1759" t="n">
-        <v>4.94999980926514</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F1759"/>
       <c r="G1759" t="s">
-        <v>684</v>
+        <v>713</v>
       </c>
       <c r="H1759" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="1" t="n">
+        <v>46101.6912384259</v>
+      </c>
+      <c r="B1760" t="n">
+        <v>4559253</v>
+      </c>
+      <c r="C1760" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D1760" t="n">
+        <v>4.95499992370605</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>4.96999979019165</v>
+      </c>
+      <c r="G1760" t="s">
+        <v>681</v>
+      </c>
+      <c r="H1760" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -48214,9 +48214,11 @@
       <c r="E1759" t="n">
         <v>5</v>
       </c>
-      <c r="F1759"/>
+      <c r="F1759" t="n">
+        <v>4.96999979019165</v>
+      </c>
       <c r="G1759" t="s">
-        <v>713</v>
+        <v>681</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48224,27 +48226,51 @@
     </row>
     <row r="1760">
       <c r="A1760" s="1" t="n">
-        <v>46101.6912384259</v>
+        <v>46104.3333333333</v>
       </c>
       <c r="B1760" t="n">
-        <v>4559253</v>
+        <v>114502</v>
       </c>
       <c r="C1760" t="n">
-        <v>5.01999998092651</v>
+        <v>5</v>
       </c>
       <c r="D1760" t="n">
-        <v>4.95499992370605</v>
+        <v>4.98999977111816</v>
       </c>
       <c r="E1760" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="F1760"/>
+      <c r="G1760" t="s">
+        <v>713</v>
+      </c>
+      <c r="H1760" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="1" t="n">
+        <v>46104.6912384259</v>
+      </c>
+      <c r="B1761" t="n">
+        <v>114502</v>
+      </c>
+      <c r="C1761" t="n">
         <v>5</v>
       </c>
-      <c r="F1760" t="n">
-        <v>4.96999979019165</v>
-      </c>
-      <c r="G1760" t="s">
-        <v>681</v>
-      </c>
-      <c r="H1760" t="s">
+      <c r="D1761" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="E1761" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="F1761" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1761" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1761" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -48240,9 +48240,11 @@
       <c r="E1760" t="n">
         <v>4.98999977111816</v>
       </c>
-      <c r="F1760"/>
+      <c r="F1760" t="n">
+        <v>5</v>
+      </c>
       <c r="G1760" t="s">
-        <v>713</v>
+        <v>682</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48250,10 +48252,10 @@
     </row>
     <row r="1761">
       <c r="A1761" s="1" t="n">
-        <v>46104.6912384259</v>
+        <v>46105.3333333333</v>
       </c>
       <c r="B1761" t="n">
-        <v>114502</v>
+        <v>11418</v>
       </c>
       <c r="C1761" t="n">
         <v>5</v>
@@ -48264,13 +48266,37 @@
       <c r="E1761" t="n">
         <v>4.98999977111816</v>
       </c>
-      <c r="F1761" t="n">
+      <c r="F1761"/>
+      <c r="G1761" t="s">
+        <v>713</v>
+      </c>
+      <c r="H1761" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="1" t="n">
+        <v>46105.6909722222</v>
+      </c>
+      <c r="B1762" t="n">
+        <v>11418</v>
+      </c>
+      <c r="C1762" t="n">
         <v>5</v>
       </c>
-      <c r="G1761" t="s">
-        <v>682</v>
-      </c>
-      <c r="H1761" t="s">
+      <c r="D1762" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="E1762" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="F1762" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="G1762" t="s">
+        <v>686</v>
+      </c>
+      <c r="H1762" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -48266,9 +48266,11 @@
       <c r="E1761" t="n">
         <v>4.98999977111816</v>
       </c>
-      <c r="F1761"/>
+      <c r="F1761" t="n">
+        <v>4.99499988555908</v>
+      </c>
       <c r="G1761" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48276,10 +48278,10 @@
     </row>
     <row r="1762">
       <c r="A1762" s="1" t="n">
-        <v>46105.6909722222</v>
+        <v>46106.3333333333</v>
       </c>
       <c r="B1762" t="n">
-        <v>11418</v>
+        <v>78233</v>
       </c>
       <c r="C1762" t="n">
         <v>5</v>
@@ -48288,15 +48290,39 @@
         <v>4.98999977111816</v>
       </c>
       <c r="E1762" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="F1762"/>
+      <c r="G1762" t="s">
+        <v>713</v>
+      </c>
+      <c r="H1762" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="1" t="n">
+        <v>46106.6912731481</v>
+      </c>
+      <c r="B1763" t="n">
+        <v>78233</v>
+      </c>
+      <c r="C1763" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1763" t="n">
         <v>4.98999977111816</v>
       </c>
-      <c r="F1762" t="n">
+      <c r="E1763" t="n">
         <v>4.99499988555908</v>
       </c>
-      <c r="G1762" t="s">
+      <c r="F1763" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="G1763" t="s">
         <v>686</v>
       </c>
-      <c r="H1762" t="s">
+      <c r="H1763" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -48292,9 +48292,11 @@
       <c r="E1762" t="n">
         <v>4.99499988555908</v>
       </c>
-      <c r="F1762"/>
+      <c r="F1762" t="n">
+        <v>4.99499988555908</v>
+      </c>
       <c r="G1762" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48302,27 +48304,51 @@
     </row>
     <row r="1763">
       <c r="A1763" s="1" t="n">
-        <v>46106.6912731481</v>
+        <v>46107.3333333333</v>
       </c>
       <c r="B1763" t="n">
-        <v>78233</v>
+        <v>21916</v>
       </c>
       <c r="C1763" t="n">
         <v>5</v>
       </c>
       <c r="D1763" t="n">
-        <v>4.98999977111816</v>
+        <v>4.99499988555908</v>
       </c>
       <c r="E1763" t="n">
         <v>4.99499988555908</v>
       </c>
-      <c r="F1763" t="n">
+      <c r="F1763"/>
+      <c r="G1763" t="s">
+        <v>713</v>
+      </c>
+      <c r="H1763" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="1" t="n">
+        <v>46107.6912384259</v>
+      </c>
+      <c r="B1764" t="n">
+        <v>21916</v>
+      </c>
+      <c r="C1764" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1764" t="n">
         <v>4.99499988555908</v>
       </c>
-      <c r="G1763" t="s">
-        <v>686</v>
-      </c>
-      <c r="H1763" t="s">
+      <c r="E1764" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="F1764" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1764" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1764" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="713">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2151,9 +2151,6 @@
   </si>
   <si>
     <t xml:space="preserve">5.07000017166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -48318,37 +48315,13 @@
       <c r="E1763" t="n">
         <v>4.99499988555908</v>
       </c>
-      <c r="F1763"/>
+      <c r="F1763" t="n">
+        <v>5</v>
+      </c>
       <c r="G1763" t="s">
-        <v>713</v>
+        <v>682</v>
       </c>
       <c r="H1763" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="1764">
-      <c r="A1764" s="1" t="n">
-        <v>46107.6912384259</v>
-      </c>
-      <c r="B1764" t="n">
-        <v>21916</v>
-      </c>
-      <c r="C1764" t="n">
-        <v>5</v>
-      </c>
-      <c r="D1764" t="n">
-        <v>4.99499988555908</v>
-      </c>
-      <c r="E1764" t="n">
-        <v>4.99499988555908</v>
-      </c>
-      <c r="F1764" t="n">
-        <v>5</v>
-      </c>
-      <c r="G1764" t="s">
-        <v>682</v>
-      </c>
-      <c r="H1764" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -48325,6 +48325,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1764">
+      <c r="A1764" s="1" t="n">
+        <v>46108.3333333333</v>
+      </c>
+      <c r="B1764" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1764" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1764" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1764" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1764" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1764" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1764" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AV.MI.xlsx
+++ b/data/AV.MI.xlsx
@@ -48351,6 +48351,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1765">
+      <c r="A1765" s="1" t="n">
+        <v>46111.2916666667</v>
+      </c>
+      <c r="B1765" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1765" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1765" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1765" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1765" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1765" t="s">
+        <v>682</v>
+      </c>
+      <c r="H1765" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
